--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1006"/>
+  <dimension ref="A1:H1008"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="47" customWidth="1" style="35" min="1" max="1"/>
@@ -600,7 +600,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G2" s="19" t="inlineStr">
+      <c r="G2" s="36" t="inlineStr">
         <is>
           <t>Auto-generated PK (Counter); internal - globally unique.
 SP engineer constructs docs URL with list_documents_url_prefix/item_id when download
@@ -644,7 +644,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G3" s="19" t="inlineStr">
+      <c r="G3" s="36" t="inlineStr">
         <is>
           <t>Auto-generated PK (Counter); internal; Globally unique</t>
         </is>
@@ -686,7 +686,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G4" s="19" t="inlineStr">
+      <c r="G4" s="36" t="inlineStr">
         <is>
           <t>unique number for work-item/deliverable/task (equivalent of delivery_item_id in hilda); immutable;</t>
         </is>
@@ -760,7 +760,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G6" s="19" t="inlineStr">
+      <c r="G6" s="36" t="inlineStr">
         <is>
           <t>e.g. OMADM FOTA IOT report; rare to change post-template-load. actual work-item description.</t>
         </is>
@@ -797,7 +797,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G7" s="19" t="inlineStr">
+      <c r="G7" s="36" t="inlineStr">
         <is>
           <t>{confirmation, test_tech_waiver_report, compliance_certification_release_notes, default}
 delivery_item_type : what type of document being delivered</t>
@@ -835,7 +835,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G8" s="19" t="inlineStr">
+      <c r="G8" s="36" t="inlineStr">
         <is>
           <t>11-value Choice (Not Started, Open, OutreachSent, DocumentReceived, UnderPMReview, OwnerClosed, Delayed, Blocked, ReadyForSubmission, SubmittedToCustomer, Closed). list-value = 'Not Started' is SP-side state for TPM-loaded-template-not-yet-started-tracking;
 SP UI engineer uses this field to show start collection button, close all items button in milestone view, display approve button, send reminder button, documents button in per-work-item view</t>
@@ -1017,7 +1017,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G13" s="19" t="inlineStr">
+      <c r="G13" s="36" t="inlineStr">
         <is>
           <t>HILDA auto-populated from inbound owner replies; TPM read-only</t>
         </is>
@@ -1054,7 +1054,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G14" s="19" t="inlineStr">
+      <c r="G14" s="36" t="inlineStr">
         <is>
           <t>resolved from owner_corp-usa_email ; if owner_corp-usa_email l is NA, field is empty</t>
         </is>
@@ -1091,7 +1091,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G15" s="19" t="inlineStr">
+      <c r="G15" s="36" t="inlineStr">
         <is>
           <t>Cannot be type free text; email should resolve to corp AD Name owner_name</t>
         </is>
@@ -1128,7 +1128,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G16" s="19" t="inlineStr">
+      <c r="G16" s="36" t="inlineStr">
         <is>
           <t>free type text (typically used for non-USA owners)</t>
         </is>
@@ -1165,7 +1165,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G17" s="19" t="inlineStr">
+      <c r="G17" s="36" t="inlineStr">
         <is>
           <t>If owner_corp_email is available,  the part before '@' is the value. TPM  can type free text;</t>
         </is>
@@ -1235,7 +1235,7 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="G19" s="19" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
         <is>
           <t>PLM issue URL; when PLM link button in per-work-item view is clicked, SP UI engineer usess this field to open URL in new browser tab</t>
         </is>
@@ -1272,7 +1272,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G20" s="19" t="inlineStr">
+      <c r="G20" s="36" t="inlineStr">
         <is>
           <t>Free-form TPM commentary; TPM-editable inline</t>
         </is>
@@ -1309,7 +1309,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G21" s="19" t="inlineStr">
+      <c r="G21" s="36" t="inlineStr">
         <is>
           <t>MultiChoice {Email, CorporateMessenger, CorporatePLM, NetworkSharedDrive, Customer JIRA, SPUI} ]</t>
         </is>
@@ -1346,7 +1346,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G22" s="19" t="n"/>
+      <c r="G22" s="36" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
@@ -1411,7 +1411,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G24" s="19" t="inlineStr">
+      <c r="G24" s="36" t="inlineStr">
         <is>
           <t>e.g. SW PL, HW PL</t>
         </is>
@@ -1448,7 +1448,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G25" s="19" t="inlineStr">
+      <c r="G25" s="36" t="inlineStr">
         <is>
           <t>free form type text; email-alias is not CORP AD accounts; HILDA uses this to discover actual owners;</t>
         </is>
@@ -1485,7 +1485,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G26" s="19" t="inlineStr">
+      <c r="G26" s="36" t="inlineStr">
         <is>
           <t>resolved from tg_owner_corp-usa_email; HILDA uses this to discover actual owners</t>
         </is>
@@ -1522,7 +1522,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G27" s="19" t="inlineStr">
+      <c r="G27" s="36" t="inlineStr">
         <is>
           <t>Cannot be type free text; email should resolve to corp AD Name owner_name; HILDA uses this to discover actual owners</t>
         </is>
@@ -1559,7 +1559,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G28" s="19" t="inlineStr">
+      <c r="G28" s="36" t="inlineStr">
         <is>
           <t>HILDA uses this to discover actual owners</t>
         </is>
@@ -1860,7 +1860,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G37" s="19" t="inlineStr">
+      <c r="G37" s="36" t="inlineStr">
         <is>
           <t>for hilda purposes only; Internal slug for path construction
 (\NSD1\internal\&lt;carrier&gt;\&lt;device&gt;\&lt;milestone&gt;\&lt;tg&gt;\&lt;item_path_slug&gt;\&lt;doc_type&gt;)</t>
@@ -1898,7 +1898,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G38" s="19" t="n"/>
+      <c r="G38" s="36" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
@@ -1931,7 +1931,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G39" s="19" t="inlineStr">
+      <c r="G39" s="36" t="inlineStr">
         <is>
           <t>HILDA auto-set on OwnerClosed state</t>
         </is>
@@ -1968,7 +1968,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G40" s="19" t="inlineStr">
+      <c r="G40" s="36" t="inlineStr">
         <is>
           <t>for hilda internal purposes only (not for TPM or SP UI engineer)</t>
         </is>
@@ -2005,7 +2005,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G41" s="19" t="inlineStr">
+      <c r="G41" s="36" t="inlineStr">
         <is>
           <t>values {GoogleDrive, Email, Customer tracking system}; type of system to which documents are uploaded</t>
         </is>
@@ -2042,7 +2042,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G42" s="19" t="inlineStr">
+      <c r="G42" s="36" t="inlineStr">
         <is>
           <t xml:space="preserve">e.g. actual google drive URL for Google drive customer_Delivery_modality; </t>
         </is>
@@ -2079,7 +2079,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G43" s="19" t="inlineStr">
+      <c r="G43" s="36" t="inlineStr">
         <is>
           <t>Internal credential reference, never displayed</t>
         </is>
@@ -2116,7 +2116,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G44" s="19" t="inlineStr">
+      <c r="G44" s="36" t="inlineStr">
         <is>
           <t>HILDA-managed (set on outreach email sent to ownerss)</t>
         </is>
@@ -2153,7 +2153,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G45" s="19" t="inlineStr">
+      <c r="G45" s="36" t="inlineStr">
         <is>
           <t>SP UI engineer modifies this field when send reminder button is
 clicked in work-item view, triggers SP Alert email to HILDA</t>
@@ -2163,12 +2163,12 @@
     <row r="46" ht="15.75" customHeight="1" s="35">
       <c r="A46" s="11" t="inlineStr">
         <is>
-          <t>doc_count</t>
+          <t>reminder_count</t>
         </is>
       </c>
       <c r="B46" s="11" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C46" s="6" t="inlineStr">
@@ -2191,21 +2191,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G46" s="21" t="inlineStr">
-        <is>
-          <t>for hilda purposes only</t>
+      <c r="G46" s="36" t="inlineStr">
+        <is>
+          <t>HILDA-managed integer column. Default = 0. Incremented atomically by HILDA when a reminder or escalation dispatches successfully (FR-10 rule-engine reminders + FR-65 TPM-initiated reminders both count). Reset to 0 on owner response per FR-12 (or per-(BATCH-id) round per FR-9 batch semantics). Used by FR-10 escalation trigger: reminder_count &gt;= M plus last_owner_response_at older than threshold. SP UI engineer does NOT read or write this column.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" s="35">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>last_owner_response_at</t>
         </is>
       </c>
       <c r="B47" s="11" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>DATE/TIME</t>
         </is>
       </c>
       <c r="C47" s="6" t="inlineStr">
@@ -2228,21 +2228,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G47" s="21" t="inlineStr">
-        <is>
-          <t>(pending / complete / not_required); for hilda purposes only</t>
+      <c r="G47" s="36" t="inlineStr">
+        <is>
+          <t>HILDA-managed datetime column. Set by FR-12 inbound email parsing when ANY status or comment update from the owner is processed (NOT set by HILDA-side writes — decouples from SP system Modified column which flips on every HILDA write). Used by FR-10 escalation trigger as the 'no response' signal. NULL until first owner response. SP UI engineer does NOT read or write this column.</t>
         </is>
       </c>
     </row>
     <row r="48" ht="17.25" customHeight="1" s="35">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>ingress_folder</t>
+          <t>doc_count</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
@@ -2265,21 +2265,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G48" s="18" t="inlineStr">
-        <is>
-          <t>for hilda purposes only; e.g. \carrierX\deviceY\milestoneZ\WiFi_Conformance\</t>
+      <c r="G48" s="21" t="inlineStr">
+        <is>
+          <t>for hilda purposes only</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" s="35">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>target_folder</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2302,21 +2302,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G49" s="22" t="inlineStr">
-        <is>
-          <t>for hilda purposes only; e.g. drive.google.com\vzw\SM-S901U</t>
+      <c r="G49" s="21" t="inlineStr">
+        <is>
+          <t>(pending / complete / not_required); for hilda purposes only</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17.25" customHeight="1" s="35">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>pm_approval_at</t>
+          <t>ingress_folder</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2329,9 +2329,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -2341,14 +2341,14 @@
       </c>
       <c r="G50" s="18" t="inlineStr">
         <is>
-          <t>When TPM approves a work item, SP UI engineer updates this field</t>
+          <t>for hilda purposes only; e.g. \carrierX\deviceY\milestoneZ\WiFi_Conformance\</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1" s="35">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>pm_approval_pm_id</t>
+          <t>target_folder</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -2366,9 +2366,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -2376,21 +2376,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G51" s="18" t="inlineStr">
-        <is>
-          <t>When TPM approves a work item, SP UI engineer updates this field</t>
+      <c r="G51" s="22" t="inlineStr">
+        <is>
+          <t>for hilda purposes only; e.g. drive.google.com\vzw\SM-S901U</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20.25" customHeight="1" s="35">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>tpm_reassignment_target_item_id</t>
+          <t>pm_approval_at</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>DATE/TIME</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -2403,9 +2403,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E52" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E52" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2415,14 +2415,14 @@
       </c>
       <c r="G52" s="18" t="inlineStr">
         <is>
-          <t>for hilda internal purposes only; resets work-item id of a document;</t>
+          <t>When TPM approves a work item, SP UI engineer updates this field</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1" s="35">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>tpm_resolved_doc_type</t>
+          <t>pm_approval_pm_id</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
@@ -2440,9 +2440,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E53" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E53" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -2452,19 +2452,19 @@
       </c>
       <c r="G53" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">for hilda internal purposes only; resolves document type of a document; </t>
+          <t>When TPM approves a work item, SP UI engineer updates this field</t>
         </is>
       </c>
     </row>
     <row r="54" ht="32.25" customHeight="1" s="35">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>tpm_revision_resolution</t>
+          <t>tpm_reassignment_target_item_id</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -2489,416 +2489,416 @@
       </c>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t>for hilda internal purposes only; resolves new/revised revision of a document;</t>
+          <t>for hilda internal purposes only; resets work-item id of a document;</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="35">
       <c r="A55" s="11" t="inlineStr">
         <is>
+          <t>tpm_resolved_doc_type</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G55" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">for hilda internal purposes only; resolves document type of a document; </t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" s="35">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>tpm_revision_resolution</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G56" s="18" t="inlineStr">
+        <is>
+          <t>for hilda internal purposes only; resolves new/revised revision of a document;</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" s="35">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
           <t>ingress_nsd (denorm TG)</t>
         </is>
       </c>
-      <c r="B55" s="11" t="inlineStr">
+      <c r="B57" s="11" t="inlineStr">
         <is>
           <t>LIST</t>
         </is>
       </c>
-      <c r="C55" s="6" t="inlineStr">
+      <c r="C57" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D55" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E55" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G55" s="18" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
         <is>
           <t>list values: NSD1, NSD2, none
 (two different network shared drives that different TGs use)</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="15.75" customHeight="1" s="35">
-      <c r="A56" s="11" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>list_documents_url_prefix (ideal storage
  is in SP Java script config, not here)</t>
         </is>
       </c>
-      <c r="B56" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="C56" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D56" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E56" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F56" s="8" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F58" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G56" s="20" t="inlineStr">
+      <c r="G58" s="20" t="inlineStr">
         <is>
           <t>SP constructs docs URL with list_documents_url_prefix/item_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" s="35">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>folder_routing_enabled (denorm)</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="inlineStr">
-        <is>
-          <t>BOOL</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
-        </is>
-      </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G57" s="19" t="inlineStr">
-        <is>
-          <t>hilda internal purposes; TGs using network shared drives to deliver documents</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
-        <is>
-          <t>per_item_rule_overrides</t>
-        </is>
-      </c>
-      <c r="B58" s="11" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="C58" s="6" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
-        </is>
-      </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G58" s="19" t="inlineStr">
-        <is>
-          <t>for hilda purposes only; Ph-2 placeholder - August 1' 2026 delivery.</t>
         </is>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" s="35">
       <c r="A59" s="11" t="inlineStr">
         <is>
+          <t>folder_routing_enabled (denorm)</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>BOOL</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G59" s="36" t="inlineStr">
+        <is>
+          <t>hilda internal purposes; TGs using network shared drives to deliver documents</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" s="35">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>per_item_rule_overrides</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G60" s="36" t="inlineStr">
+        <is>
+          <t>for hilda purposes only; Ph-2 placeholder - August 1' 2026 delivery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" s="35">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
           <t>sort_order</t>
         </is>
       </c>
-      <c r="B59" s="11" t="n"/>
-      <c r="C59" s="23" t="inlineStr">
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="23" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G59" s="19" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G61" s="36" t="inlineStr">
         <is>
           <t>Controls display order; not a visible column</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="15.75" customHeight="1" s="35">
-      <c r="A60" s="25" t="n"/>
-      <c r="B60" s="11" t="n"/>
-      <c r="C60" s="25" t="n"/>
-      <c r="D60" s="25" t="n"/>
-      <c r="E60" s="34" t="n"/>
-      <c r="F60" s="34" t="n"/>
-      <c r="G60" s="34" t="n"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" s="35">
-      <c r="A61" s="27" t="inlineStr">
+    <row r="62" ht="15.75" customHeight="1" s="35">
+      <c r="A62" s="25" t="n"/>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="25" t="n"/>
+      <c r="D62" s="25" t="n"/>
+      <c r="E62" s="34" t="n"/>
+      <c r="F62" s="34" t="n"/>
+      <c r="G62" s="34" t="n"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" s="35">
+      <c r="A63" s="27" t="inlineStr">
         <is>
           <t>Milestone SP List
 * clean separation from delivery items, avoid hacks</t>
         </is>
       </c>
-      <c r="B61" s="29" t="n"/>
-      <c r="C61" s="29" t="n"/>
-      <c r="D61" s="29" t="n"/>
-      <c r="E61" s="20" t="n"/>
-      <c r="F61" s="20" t="n"/>
-      <c r="G61" s="20" t="n"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" s="35">
-      <c r="A62" s="29" t="inlineStr">
-        <is>
-          <t>milestone_id</t>
-        </is>
-      </c>
-      <c r="B62" s="11" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="C62" s="14" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D62" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E62" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F62" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G62" s="20" t="inlineStr">
-        <is>
-          <t>primary key</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" s="35">
-      <c r="A63" s="29" t="inlineStr">
-        <is>
-          <t>status</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="inlineStr">
-        <is>
-          <t>LIST</t>
-        </is>
-      </c>
-      <c r="C63" s="14" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D63" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E63" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F63" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G63" s="20" t="inlineStr">
-        <is>
-          <t>list-values {Not Started, In Progress, Completed, Delayed}, SP engineer uses this to check if start collection button to be displayed in milestone view</t>
-        </is>
-      </c>
+      <c r="B63" s="29" t="n"/>
+      <c r="C63" s="29" t="n"/>
+      <c r="D63" s="29" t="n"/>
+      <c r="E63" s="20" t="n"/>
+      <c r="F63" s="20" t="n"/>
+      <c r="G63" s="20" t="n"/>
     </row>
     <row r="64" ht="15.75" customHeight="1" s="35">
       <c r="A64" s="29" t="inlineStr">
         <is>
+          <t>milestone_id</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="C64" s="14" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G64" s="20" t="inlineStr">
+        <is>
+          <t>primary key</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" s="35">
+      <c r="A65" s="29" t="inlineStr">
+        <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="inlineStr">
+        <is>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="C65" s="14" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G65" s="20" t="inlineStr">
+        <is>
+          <t>list-values {Not Started, In Progress, Completed, Delayed}, SP engineer uses this to check if start collection button to be displayed in milestone view</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" s="35">
+      <c r="A66" s="29" t="inlineStr">
+        <is>
           <t>download_package_request_timestamp</t>
         </is>
       </c>
-      <c r="B64" s="11" t="inlineStr">
+      <c r="B66" s="11" t="inlineStr">
         <is>
           <t>DATE/TIME</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C66" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G64" s="20" t="inlineStr">
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G66" s="20" t="inlineStr">
         <is>
           <t>SP engineer writes when TPM clicks Download Package button.
 The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15.75" customHeight="1" s="35">
-      <c r="A65" s="29" t="inlineStr">
-        <is>
-          <t>download_package_status</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="inlineStr">
-        <is>
-          <t>LIST</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D65" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E65" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G65" s="20" t="inlineStr">
-        <is>
-          <t>HILDA-write. Enum: preparing | ready | failed. Set to preparing immediately by SP UI on click (mirror of request_timestamp); HILDA writes ready on assembly success / failed on assembly error. SP web part reads this on focus-aware refresh to decide whether to show "Preparing..." indicator or Download Now link</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" s="35">
-      <c r="A66" s="29" t="inlineStr">
-        <is>
-          <t>download_package_url</t>
-        </is>
-      </c>
-      <c r="B66" s="11" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="C66" s="6" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F66" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G66" s="20" t="inlineStr">
-        <is>
-          <t>HILDA-write. The scoped download URL https://hilda-proxy.corp/dl/&lt;scoped_token&gt; HILDA generates when assembly succeeds. The clickable target of the Download Now link. Null until status=ready</t>
-        </is>
-      </c>
-    </row>
     <row r="67" ht="15.75" customHeight="1" s="35">
       <c r="A67" s="29" t="inlineStr">
         <is>
-          <t>download_package_generated_at</t>
+          <t>download_package_status</t>
         </is>
       </c>
       <c r="B67" s="11" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
-        </is>
-      </c>
-      <c r="C67" s="6" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr">
+        <is>
+          <t>must_show</t>
         </is>
       </c>
       <c r="D67" s="7" t="inlineStr">
@@ -2906,31 +2906,31 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E67" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F67" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E67" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F67" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="G67" s="20" t="inlineStr">
         <is>
-          <t>HILDA-write. Timestamp of assembly completion; used for cache-staleness display ("generated 3 min ago")</t>
+          <t>HILDA-write. Enum: preparing | ready | failed. Set to preparing immediately by SP UI on click (mirror of request_timestamp); HILDA writes ready on assembly success / failed on assembly error. SP web part reads this on focus-aware refresh to decide whether to show "Preparing..." indicator or Download Now link</t>
         </is>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="35">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>milestone_collection_started_at</t>
+          <t>download_package_url</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="C68" s="6" t="inlineStr">
@@ -2943,26 +2943,26 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E68" s="8" t="inlineStr">
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F68" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F68" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="G68" s="20" t="inlineStr">
         <is>
-          <t>SP engineer uses this to check if start collection button to be displayed in milestone view. SP engineer modifies this field once collection started. The act of writing this field is what fires the SP-alert email</t>
+          <t>HILDA-write. The scoped download URL https://hilda-proxy.corp/dl/&lt;scoped_token&gt; HILDA generates when assembly succeeds. The clickable target of the Download Now link. Null until status=ready</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="35">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>milestone_submission_triggered_at</t>
+          <t>download_package_generated_at</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
@@ -2980,9 +2980,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -2992,36 +2992,36 @@
       </c>
       <c r="G69" s="20" t="inlineStr">
         <is>
-          <t>SP engineer modifies this field once submit to carrier button is clicked. The act of writing this field is what fires the SP-alert email</t>
+          <t>HILDA-write. Timestamp of assembly completion; used for cache-staleness display ("generated 3 min ago")</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="35">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>milestone_collection_started_at</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C70" s="14" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D70" s="8" t="inlineStr">
+          <t>DATE/TIME</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E70" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="E70" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="F70" s="8" t="inlineStr">
         <is>
           <t>YES</t>
@@ -3029,14 +3029,14 @@
       </c>
       <c r="G70" s="20" t="inlineStr">
         <is>
-          <t>update expected_completion_date of all delivery items / work items of this milestone. The act of writing this field is what fires the SP-alert email</t>
+          <t>SP engineer uses this to check if start collection button to be displayed in milestone view. SP engineer modifies this field once collection started. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="35">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>refresh_requested_at</t>
+          <t>milestone_submission_triggered_at</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -3066,186 +3066,250 @@
       </c>
       <c r="G71" s="20" t="inlineStr">
         <is>
-          <t>SP engineer modifies this field once refresh button is clicked. The act of writing this field is what fires the SP-alert email</t>
+          <t>SP engineer modifies this field once submit to carrier button is clicked. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="35">
       <c r="A72" s="29" t="inlineStr">
         <is>
+          <t>target_date</t>
+        </is>
+      </c>
+      <c r="B72" s="11" t="inlineStr">
+        <is>
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D72" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F72" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G72" s="20" t="inlineStr">
+        <is>
+          <t>update expected_completion_date of all delivery items / work items of this milestone. The act of writing this field is what fires the SP-alert email</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" s="35">
+      <c r="A73" s="29" t="inlineStr">
+        <is>
+          <t>refresh_requested_at</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="inlineStr">
+        <is>
+          <t>DATE/TIME</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E73" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G73" s="20" t="inlineStr">
+        <is>
+          <t>SP engineer modifies this field once refresh button is clicked. The act of writing this field is what fires the SP-alert email</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" s="35">
+      <c r="A74" s="29" t="inlineStr">
+        <is>
           <t>closed_all_items_triggered_at</t>
         </is>
       </c>
-      <c r="B72" s="11" t="inlineStr">
+      <c r="B74" s="11" t="inlineStr">
         <is>
           <t>DATE/TIME</t>
         </is>
       </c>
-      <c r="C72" s="6" t="inlineStr">
+      <c r="C74" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D72" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E72" s="8" t="inlineStr">
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F72" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G72" s="20" t="inlineStr">
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" s="20" t="inlineStr">
         <is>
           <t>SP engineer modifies this field once close all items button is clicked. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1" s="35">
-      <c r="A73" s="25" t="n"/>
-      <c r="B73" s="25" t="n"/>
-      <c r="C73" s="25" t="n"/>
-      <c r="D73" s="25" t="n"/>
-      <c r="E73" s="30" t="n"/>
-      <c r="F73" s="30" t="n"/>
-      <c r="G73" s="30" t="n"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" s="35">
-      <c r="A74" s="31" t="inlineStr">
+    <row r="75" ht="15.75" customHeight="1" s="35">
+      <c r="A75" s="25" t="n"/>
+      <c r="B75" s="25" t="n"/>
+      <c r="C75" s="25" t="n"/>
+      <c r="D75" s="25" t="n"/>
+      <c r="E75" s="30" t="n"/>
+      <c r="F75" s="30" t="n"/>
+      <c r="G75" s="30" t="n"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" s="35">
+      <c r="A76" s="31" t="inlineStr">
         <is>
           <t>Customer SP list (need not be a new list, 
 need below values from customer_id)</t>
         </is>
       </c>
-      <c r="B74" s="29" t="n"/>
-      <c r="C74" s="29" t="n"/>
-      <c r="D74" s="29" t="n"/>
-      <c r="E74" s="32" t="n"/>
-      <c r="F74" s="32" t="n"/>
-      <c r="G74" s="32" t="n"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" s="35">
-      <c r="A75" s="29" t="inlineStr">
+      <c r="B76" s="29" t="n"/>
+      <c r="C76" s="29" t="n"/>
+      <c r="D76" s="29" t="n"/>
+      <c r="E76" s="32" t="n"/>
+      <c r="F76" s="32" t="n"/>
+      <c r="G76" s="32" t="n"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="35">
+      <c r="A77" s="29" t="inlineStr">
         <is>
           <t>customer_jira_url</t>
         </is>
       </c>
-      <c r="B75" s="11" t="inlineStr">
+      <c r="B77" s="11" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="C75" s="6" t="inlineStr">
+      <c r="C77" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D75" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E75" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F75" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G75" s="20" t="inlineStr">
+      <c r="D77" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E77" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F77" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G77" s="20" t="inlineStr">
         <is>
           <t>hilda internal purposes only</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="15.75" customHeight="1" s="35">
-      <c r="A76" s="33" t="n"/>
-      <c r="B76" s="33" t="n"/>
-      <c r="C76" s="33" t="n"/>
-      <c r="D76" s="33" t="n"/>
-      <c r="E76" s="33" t="n"/>
-      <c r="F76" s="33" t="n"/>
-      <c r="G76" s="33" t="n"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" s="35">
-      <c r="A77" s="31" t="inlineStr">
+    <row r="78" ht="15.75" customHeight="1" s="35">
+      <c r="A78" s="33" t="n"/>
+      <c r="B78" s="33" t="n"/>
+      <c r="C78" s="33" t="n"/>
+      <c r="D78" s="33" t="n"/>
+      <c r="E78" s="33" t="n"/>
+      <c r="F78" s="33" t="n"/>
+      <c r="G78" s="33" t="n"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" s="35">
+      <c r="A79" s="31" t="inlineStr">
         <is>
           <t>Devices SP list (need not be a new list,
 need below value from device_id)</t>
         </is>
       </c>
-      <c r="B77" s="29" t="n"/>
-      <c r="C77" s="29" t="n"/>
-      <c r="D77" s="29" t="n"/>
-      <c r="E77" s="32" t="n"/>
-      <c r="F77" s="32" t="n"/>
-      <c r="G77" s="32" t="n"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1" s="35">
-      <c r="A78" s="29" t="inlineStr">
+      <c r="B79" s="29" t="n"/>
+      <c r="C79" s="29" t="n"/>
+      <c r="D79" s="29" t="n"/>
+      <c r="E79" s="32" t="n"/>
+      <c r="F79" s="32" t="n"/>
+      <c r="G79" s="32" t="n"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="35">
+      <c r="A80" s="29" t="inlineStr">
         <is>
           <t>assigned_pm_id (SEA email address of TPM)</t>
         </is>
       </c>
-      <c r="B78" s="11" t="inlineStr">
+      <c r="B80" s="11" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="C78" s="6" t="inlineStr">
+      <c r="C80" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D78" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E78" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F78" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G78" s="20" t="inlineStr">
+      <c r="D80" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E80" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F80" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G80" s="20" t="inlineStr">
         <is>
           <t>hilda internal purposes only</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="15.75" customHeight="1" s="35">
-      <c r="A79" s="25" t="n"/>
-      <c r="B79" s="25" t="n"/>
-      <c r="C79" s="25" t="n"/>
-      <c r="D79" s="25" t="n"/>
-      <c r="E79" s="34" t="n"/>
-      <c r="F79" s="34" t="n"/>
-      <c r="G79" s="34" t="n"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" s="35">
-      <c r="A80" s="25" t="n"/>
-      <c r="B80" s="25" t="n"/>
-      <c r="C80" s="25" t="n"/>
-      <c r="D80" s="25" t="n"/>
-      <c r="E80" s="34" t="n"/>
-      <c r="F80" s="34" t="n"/>
-      <c r="G80" s="34" t="n"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" s="35"/>
+    <row r="81" ht="15.75" customHeight="1" s="35">
+      <c r="A81" s="25" t="n"/>
+      <c r="B81" s="25" t="n"/>
+      <c r="C81" s="25" t="n"/>
+      <c r="D81" s="25" t="n"/>
+      <c r="E81" s="34" t="n"/>
+      <c r="F81" s="34" t="n"/>
+      <c r="G81" s="34" t="n"/>
+    </row>
     <row r="82" ht="15.75" customHeight="1" s="35">
       <c r="A82" s="25" t="n"/>
       <c r="B82" s="25" t="n"/>
@@ -3255,15 +3319,7 @@
       <c r="F82" s="34" t="n"/>
       <c r="G82" s="34" t="n"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" s="35">
-      <c r="A83" s="25" t="n"/>
-      <c r="B83" s="25" t="n"/>
-      <c r="C83" s="25" t="n"/>
-      <c r="D83" s="25" t="n"/>
-      <c r="E83" s="34" t="n"/>
-      <c r="F83" s="34" t="n"/>
-      <c r="G83" s="34" t="n"/>
-    </row>
+    <row r="83" ht="15.75" customHeight="1" s="35"/>
     <row r="84" ht="15.75" customHeight="1" s="35">
       <c r="A84" s="25" t="n"/>
       <c r="B84" s="25" t="n"/>
@@ -11571,6 +11627,24 @@
       <c r="F1006" s="34" t="n"/>
       <c r="G1006" s="34" t="n"/>
     </row>
+    <row r="1007">
+      <c r="A1007" s="25" t="n"/>
+      <c r="B1007" s="25" t="n"/>
+      <c r="C1007" s="25" t="n"/>
+      <c r="D1007" s="25" t="n"/>
+      <c r="E1007" s="34" t="n"/>
+      <c r="F1007" s="34" t="n"/>
+      <c r="G1007" s="34" t="n"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" s="25" t="n"/>
+      <c r="B1008" s="25" t="n"/>
+      <c r="C1008" s="25" t="n"/>
+      <c r="D1008" s="25" t="n"/>
+      <c r="E1008" s="34" t="n"/>
+      <c r="F1008" s="34" t="n"/>
+      <c r="G1008" s="34" t="n"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId1"/>

--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -514,7 +514,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1008"/>
+  <dimension ref="A1:H1009"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="47" customWidth="1" style="35" min="1" max="1"/>
@@ -2237,22 +2237,22 @@
     <row r="48" ht="17.25" customHeight="1" s="35">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t>doc_count</t>
+          <t>manual_triage_required</t>
         </is>
       </c>
       <c r="B48" s="11" t="inlineStr">
         <is>
-          <t>Integer</t>
+          <t>BOOLEAN</t>
         </is>
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>not_to_be_shown</t>
+          <t>must_show</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES (TPM)</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
@@ -2262,24 +2262,24 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G48" s="21" t="inlineStr">
-        <is>
-          <t>for hilda purposes only</t>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G48" s="36" t="inlineStr">
+        <is>
+          <t>HILDA-managed boolean column. Default = FALSE. Set to TRUE by HILDA when an inbound owner reply (per FR-12) fails the rule-based + LLM classification below confidence threshold — surfaces a Manual triage flag on the PM dashboard. TPM clears (sets to FALSE) when triage is resolved (after reading the original email and writing the correct delivery_state per FR-14). SP UI engineer reads this column to surface the triage queue in the PM dashboard; SP UI engineer's web part allows TPM to clear the flag once resolved.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1" s="35">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t>review_status</t>
+          <t>doc_count</t>
         </is>
       </c>
       <c r="B49" s="11" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>Integer</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
@@ -2304,19 +2304,19 @@
       </c>
       <c r="G49" s="21" t="inlineStr">
         <is>
-          <t>(pending / complete / not_required); for hilda purposes only</t>
+          <t>for hilda purposes only</t>
         </is>
       </c>
     </row>
     <row r="50" ht="17.25" customHeight="1" s="35">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t>ingress_folder</t>
+          <t>review_status</t>
         </is>
       </c>
       <c r="B50" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>LIST</t>
         </is>
       </c>
       <c r="C50" s="6" t="inlineStr">
@@ -2339,16 +2339,16 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G50" s="18" t="inlineStr">
-        <is>
-          <t>for hilda purposes only; e.g. \carrierX\deviceY\milestoneZ\WiFi_Conformance\</t>
+      <c r="G50" s="21" t="inlineStr">
+        <is>
+          <t>(pending / complete / not_required); for hilda purposes only</t>
         </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1" s="35">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t>target_folder</t>
+          <t>ingress_folder</t>
         </is>
       </c>
       <c r="B51" s="11" t="inlineStr">
@@ -2376,21 +2376,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G51" s="22" t="inlineStr">
-        <is>
-          <t>for hilda purposes only; e.g. drive.google.com\vzw\SM-S901U</t>
+      <c r="G51" s="18" t="inlineStr">
+        <is>
+          <t>for hilda purposes only; e.g. \carrierX\deviceY\milestoneZ\WiFi_Conformance\</t>
         </is>
       </c>
     </row>
     <row r="52" ht="20.25" customHeight="1" s="35">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t>pm_approval_at</t>
+          <t>target_folder</t>
         </is>
       </c>
       <c r="B52" s="11" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="C52" s="6" t="inlineStr">
@@ -2403,9 +2403,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E52" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -2413,21 +2413,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G52" s="18" t="inlineStr">
-        <is>
-          <t>When TPM approves a work item, SP UI engineer updates this field</t>
+      <c r="G52" s="22" t="inlineStr">
+        <is>
+          <t>for hilda purposes only; e.g. drive.google.com\vzw\SM-S901U</t>
         </is>
       </c>
     </row>
     <row r="53" ht="18.75" customHeight="1" s="35">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t>pm_approval_pm_id</t>
+          <t>pm_approval_at</t>
         </is>
       </c>
       <c r="B53" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>DATE/TIME</t>
         </is>
       </c>
       <c r="C53" s="6" t="inlineStr">
@@ -2459,12 +2459,12 @@
     <row r="54" ht="32.25" customHeight="1" s="35">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t>tpm_reassignment_target_item_id</t>
+          <t>pm_approval_pm_id</t>
         </is>
       </c>
       <c r="B54" s="11" t="inlineStr">
         <is>
-          <t>INTEGER</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="C54" s="6" t="inlineStr">
@@ -2477,9 +2477,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E54" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E54" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -2489,19 +2489,19 @@
       </c>
       <c r="G54" s="18" t="inlineStr">
         <is>
-          <t>for hilda internal purposes only; resets work-item id of a document;</t>
+          <t>When TPM approves a work item, SP UI engineer updates this field</t>
         </is>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" s="35">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t>tpm_resolved_doc_type</t>
+          <t>tpm_reassignment_target_item_id</t>
         </is>
       </c>
       <c r="B55" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C55" s="6" t="inlineStr">
@@ -2526,14 +2526,14 @@
       </c>
       <c r="G55" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">for hilda internal purposes only; resolves document type of a document; </t>
+          <t>for hilda internal purposes only; resets work-item id of a document;</t>
         </is>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" s="35">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t>tpm_revision_resolution</t>
+          <t>tpm_resolved_doc_type</t>
         </is>
       </c>
       <c r="B56" s="11" t="inlineStr">
@@ -2563,132 +2563,132 @@
       </c>
       <c r="G56" s="18" t="inlineStr">
         <is>
-          <t>for hilda internal purposes only; resolves new/revised revision of a document;</t>
+          <t xml:space="preserve">for hilda internal purposes only; resolves document type of a document; </t>
         </is>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" s="35">
       <c r="A57" s="11" t="inlineStr">
         <is>
+          <t>tpm_revision_resolution</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G57" s="18" t="inlineStr">
+        <is>
+          <t>for hilda internal purposes only; resolves new/revised revision of a document;</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
           <t>ingress_nsd (denorm TG)</t>
         </is>
       </c>
-      <c r="B57" s="11" t="inlineStr">
+      <c r="B58" s="11" t="inlineStr">
         <is>
           <t>LIST</t>
         </is>
       </c>
-      <c r="C57" s="6" t="inlineStr">
+      <c r="C58" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D57" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E57" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G57" s="18" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G58" s="18" t="inlineStr">
         <is>
           <t>list values: NSD1, NSD2, none
 (two different network shared drives that different TGs use)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="11" t="inlineStr">
+    <row r="59" ht="15.75" customHeight="1" s="35">
+      <c r="A59" s="11" t="inlineStr">
         <is>
           <t>list_documents_url_prefix (ideal storage
  is in SP Java script config, not here)</t>
         </is>
       </c>
-      <c r="B58" s="11" t="inlineStr">
+      <c r="B59" s="11" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="C58" s="6" t="inlineStr">
+      <c r="C59" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D58" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E58" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F58" s="8" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F59" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G58" s="20" t="inlineStr">
+      <c r="G59" s="20" t="inlineStr">
         <is>
           <t>SP constructs docs URL with list_documents_url_prefix/item_id</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" s="35">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>folder_routing_enabled (denorm)</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="inlineStr">
-        <is>
-          <t>BOOL</t>
-        </is>
-      </c>
-      <c r="C59" s="6" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
-        </is>
-      </c>
-      <c r="D59" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E59" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F59" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G59" s="36" t="inlineStr">
-        <is>
-          <t>hilda internal purposes; TGs using network shared drives to deliver documents</t>
         </is>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" s="35">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t>per_item_rule_overrides</t>
+          <t>folder_routing_enabled (denorm)</t>
         </is>
       </c>
       <c r="B60" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>BOOL</t>
         </is>
       </c>
       <c r="C60" s="6" t="inlineStr">
@@ -2713,112 +2713,112 @@
       </c>
       <c r="G60" s="36" t="inlineStr">
         <is>
-          <t>for hilda purposes only; Ph-2 placeholder - August 1' 2026 delivery.</t>
+          <t>hilda internal purposes; TGs using network shared drives to deliver documents</t>
         </is>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" s="35">
       <c r="A61" s="11" t="inlineStr">
         <is>
+          <t>per_item_rule_overrides</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G61" s="36" t="inlineStr">
+        <is>
+          <t>for hilda purposes only; Ph-2 placeholder - August 1' 2026 delivery.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" s="35">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
           <t>sort_order</t>
         </is>
       </c>
-      <c r="B61" s="11" t="n"/>
-      <c r="C61" s="23" t="inlineStr">
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="23" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D61" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E61" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F61" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G61" s="36" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G62" s="36" t="inlineStr">
         <is>
           <t>Controls display order; not a visible column</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="15.75" customHeight="1" s="35">
-      <c r="A62" s="25" t="n"/>
-      <c r="B62" s="11" t="n"/>
-      <c r="C62" s="25" t="n"/>
-      <c r="D62" s="25" t="n"/>
-      <c r="E62" s="34" t="n"/>
-      <c r="F62" s="34" t="n"/>
-      <c r="G62" s="34" t="n"/>
-    </row>
     <row r="63" ht="15.75" customHeight="1" s="35">
-      <c r="A63" s="27" t="inlineStr">
+      <c r="A63" s="25" t="n"/>
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="25" t="n"/>
+      <c r="D63" s="25" t="n"/>
+      <c r="E63" s="34" t="n"/>
+      <c r="F63" s="34" t="n"/>
+      <c r="G63" s="34" t="n"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" s="35">
+      <c r="A64" s="27" t="inlineStr">
         <is>
           <t>Milestone SP List
 * clean separation from delivery items, avoid hacks</t>
         </is>
       </c>
-      <c r="B63" s="29" t="n"/>
-      <c r="C63" s="29" t="n"/>
-      <c r="D63" s="29" t="n"/>
-      <c r="E63" s="20" t="n"/>
-      <c r="F63" s="20" t="n"/>
-      <c r="G63" s="20" t="n"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" s="35">
-      <c r="A64" s="29" t="inlineStr">
-        <is>
-          <t>milestone_id</t>
-        </is>
-      </c>
-      <c r="B64" s="11" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D64" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E64" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F64" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G64" s="20" t="inlineStr">
-        <is>
-          <t>primary key</t>
-        </is>
-      </c>
+      <c r="B64" s="29" t="n"/>
+      <c r="C64" s="29" t="n"/>
+      <c r="D64" s="29" t="n"/>
+      <c r="E64" s="20" t="n"/>
+      <c r="F64" s="20" t="n"/>
+      <c r="G64" s="20" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="35">
       <c r="A65" s="29" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>milestone_id</t>
         </is>
       </c>
       <c r="B65" s="11" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
@@ -2836,106 +2836,106 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="F65" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G65" s="20" t="inlineStr">
         <is>
-          <t>list-values {Not Started, In Progress, Completed, Delayed}, SP engineer uses this to check if start collection button to be displayed in milestone view</t>
+          <t>primary key</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="35">
       <c r="A66" s="29" t="inlineStr">
         <is>
+          <t>status</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="inlineStr">
+        <is>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="C66" s="14" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G66" s="20" t="inlineStr">
+        <is>
+          <t>list-values {Not Started, In Progress, Completed, Delayed}, SP engineer uses this to check if start collection button to be displayed in milestone view</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" s="35">
+      <c r="A67" s="29" t="inlineStr">
+        <is>
           <t>download_package_request_timestamp</t>
         </is>
       </c>
-      <c r="B66" s="11" t="inlineStr">
+      <c r="B67" s="11" t="inlineStr">
         <is>
           <t>DATE/TIME</t>
         </is>
       </c>
-      <c r="C66" s="6" t="inlineStr">
+      <c r="C67" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E66" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F66" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G66" s="20" t="inlineStr">
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G67" s="20" t="inlineStr">
         <is>
           <t>SP engineer writes when TPM clicks Download Package button.
 The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="15.75" customHeight="1" s="35">
-      <c r="A67" s="29" t="inlineStr">
-        <is>
-          <t>download_package_status</t>
-        </is>
-      </c>
-      <c r="B67" s="11" t="inlineStr">
-        <is>
-          <t>LIST</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D67" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E67" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F67" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G67" s="20" t="inlineStr">
-        <is>
-          <t>HILDA-write. Enum: preparing | ready | failed. Set to preparing immediately by SP UI on click (mirror of request_timestamp); HILDA writes ready on assembly success / failed on assembly error. SP web part reads this on focus-aware refresh to decide whether to show "Preparing..." indicator or Download Now link</t>
-        </is>
-      </c>
-    </row>
     <row r="68" ht="15.75" customHeight="1" s="35">
       <c r="A68" s="29" t="inlineStr">
         <is>
-          <t>download_package_url</t>
+          <t>download_package_status</t>
         </is>
       </c>
       <c r="B68" s="11" t="inlineStr">
         <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="C68" s="6" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="inlineStr">
+        <is>
+          <t>must_show</t>
         </is>
       </c>
       <c r="D68" s="7" t="inlineStr">
@@ -2943,9 +2943,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E68" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E68" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="F68" s="8" t="inlineStr">
@@ -2955,19 +2955,19 @@
       </c>
       <c r="G68" s="20" t="inlineStr">
         <is>
-          <t>HILDA-write. The scoped download URL https://hilda-proxy.corp/dl/&lt;scoped_token&gt; HILDA generates when assembly succeeds. The clickable target of the Download Now link. Null until status=ready</t>
+          <t>HILDA-write. Enum: preparing | ready | failed. Set to preparing immediately by SP UI on click (mirror of request_timestamp); HILDA writes ready on assembly success / failed on assembly error. SP web part reads this on focus-aware refresh to decide whether to show "Preparing..." indicator or Download Now link</t>
         </is>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="35">
       <c r="A69" s="29" t="inlineStr">
         <is>
-          <t>download_package_generated_at</t>
+          <t>download_package_url</t>
         </is>
       </c>
       <c r="B69" s="11" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="C69" s="6" t="inlineStr">
@@ -2985,21 +2985,21 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="F69" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="F69" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="G69" s="20" t="inlineStr">
         <is>
-          <t>HILDA-write. Timestamp of assembly completion; used for cache-staleness display ("generated 3 min ago")</t>
+          <t>HILDA-write. The scoped download URL https://hilda-proxy.corp/dl/&lt;scoped_token&gt; HILDA generates when assembly succeeds. The clickable target of the Download Now link. Null until status=ready</t>
         </is>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="35">
       <c r="A70" s="29" t="inlineStr">
         <is>
-          <t>milestone_collection_started_at</t>
+          <t>download_package_generated_at</t>
         </is>
       </c>
       <c r="B70" s="11" t="inlineStr">
@@ -3017,26 +3017,26 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E70" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="F70" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G70" s="20" t="inlineStr">
         <is>
-          <t>SP engineer uses this to check if start collection button to be displayed in milestone view. SP engineer modifies this field once collection started. The act of writing this field is what fires the SP-alert email</t>
+          <t>HILDA-write. Timestamp of assembly completion; used for cache-staleness display ("generated 3 min ago")</t>
         </is>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="35">
       <c r="A71" s="29" t="inlineStr">
         <is>
-          <t>milestone_submission_triggered_at</t>
+          <t>milestone_collection_started_at</t>
         </is>
       </c>
       <c r="B71" s="11" t="inlineStr">
@@ -3059,256 +3059,284 @@
           <t>YES</t>
         </is>
       </c>
-      <c r="F71" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="F71" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="G71" s="20" t="inlineStr">
         <is>
-          <t>SP engineer modifies this field once submit to carrier button is clicked. The act of writing this field is what fires the SP-alert email</t>
+          <t>SP engineer uses this to check if start collection button to be displayed in milestone view. SP engineer modifies this field once collection started. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1" s="35">
       <c r="A72" s="29" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>milestone_submission_triggered_at</t>
         </is>
       </c>
       <c r="B72" s="11" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D72" s="8" t="inlineStr">
+          <t>DATE/TIME</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="E72" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F72" s="8" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G72" s="20" t="inlineStr">
         <is>
-          <t>update expected_completion_date of all delivery items / work items of this milestone. The act of writing this field is what fires the SP-alert email</t>
+          <t>SP engineer modifies this field once submit to carrier button is clicked. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" s="35">
       <c r="A73" s="29" t="inlineStr">
         <is>
-          <t>refresh_requested_at</t>
+          <t>target_date</t>
         </is>
       </c>
       <c r="B73" s="11" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
-        </is>
-      </c>
-      <c r="C73" s="6" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
-        </is>
-      </c>
-      <c r="D73" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C73" s="14" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D73" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F73" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F73" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="G73" s="20" t="inlineStr">
         <is>
-          <t>SP engineer modifies this field once refresh button is clicked. The act of writing this field is what fires the SP-alert email</t>
+          <t>update expected_completion_date of all delivery items / work items of this milestone. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" s="35">
       <c r="A74" s="29" t="inlineStr">
         <is>
+          <t>refresh_requested_at</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="inlineStr">
+        <is>
+          <t>DATE/TIME</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G74" s="20" t="inlineStr">
+        <is>
+          <t>SP engineer modifies this field once refresh button is clicked. The act of writing this field is what fires the SP-alert email</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" s="35">
+      <c r="A75" s="29" t="inlineStr">
+        <is>
           <t>closed_all_items_triggered_at</t>
         </is>
       </c>
-      <c r="B74" s="11" t="inlineStr">
+      <c r="B75" s="11" t="inlineStr">
         <is>
           <t>DATE/TIME</t>
         </is>
       </c>
-      <c r="C74" s="6" t="inlineStr">
+      <c r="C75" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D74" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E75" s="8" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F74" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G74" s="20" t="inlineStr">
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G75" s="20" t="inlineStr">
         <is>
           <t>SP engineer modifies this field once close all items button is clicked. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="15.75" customHeight="1" s="35">
-      <c r="A75" s="25" t="n"/>
-      <c r="B75" s="25" t="n"/>
-      <c r="C75" s="25" t="n"/>
-      <c r="D75" s="25" t="n"/>
-      <c r="E75" s="30" t="n"/>
-      <c r="F75" s="30" t="n"/>
-      <c r="G75" s="30" t="n"/>
-    </row>
     <row r="76" ht="15.75" customHeight="1" s="35">
-      <c r="A76" s="31" t="inlineStr">
+      <c r="A76" s="25" t="n"/>
+      <c r="B76" s="25" t="n"/>
+      <c r="C76" s="25" t="n"/>
+      <c r="D76" s="25" t="n"/>
+      <c r="E76" s="30" t="n"/>
+      <c r="F76" s="30" t="n"/>
+      <c r="G76" s="30" t="n"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" s="35">
+      <c r="A77" s="31" t="inlineStr">
         <is>
           <t>Customer SP list (need not be a new list, 
 need below values from customer_id)</t>
         </is>
       </c>
-      <c r="B76" s="29" t="n"/>
-      <c r="C76" s="29" t="n"/>
-      <c r="D76" s="29" t="n"/>
-      <c r="E76" s="32" t="n"/>
-      <c r="F76" s="32" t="n"/>
-      <c r="G76" s="32" t="n"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" s="35">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="B77" s="29" t="n"/>
+      <c r="C77" s="29" t="n"/>
+      <c r="D77" s="29" t="n"/>
+      <c r="E77" s="32" t="n"/>
+      <c r="F77" s="32" t="n"/>
+      <c r="G77" s="32" t="n"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" s="35">
+      <c r="A78" s="29" t="inlineStr">
         <is>
           <t>customer_jira_url</t>
         </is>
       </c>
-      <c r="B77" s="11" t="inlineStr">
+      <c r="B78" s="11" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="C77" s="6" t="inlineStr">
+      <c r="C78" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D77" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E77" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F77" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G77" s="20" t="inlineStr">
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E78" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F78" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G78" s="20" t="inlineStr">
         <is>
           <t>hilda internal purposes only</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="15.75" customHeight="1" s="35">
-      <c r="A78" s="33" t="n"/>
-      <c r="B78" s="33" t="n"/>
-      <c r="C78" s="33" t="n"/>
-      <c r="D78" s="33" t="n"/>
-      <c r="E78" s="33" t="n"/>
-      <c r="F78" s="33" t="n"/>
-      <c r="G78" s="33" t="n"/>
-    </row>
     <row r="79" ht="15.75" customHeight="1" s="35">
-      <c r="A79" s="31" t="inlineStr">
+      <c r="A79" s="33" t="n"/>
+      <c r="B79" s="33" t="n"/>
+      <c r="C79" s="33" t="n"/>
+      <c r="D79" s="33" t="n"/>
+      <c r="E79" s="33" t="n"/>
+      <c r="F79" s="33" t="n"/>
+      <c r="G79" s="33" t="n"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" s="35">
+      <c r="A80" s="31" t="inlineStr">
         <is>
           <t>Devices SP list (need not be a new list,
 need below value from device_id)</t>
         </is>
       </c>
-      <c r="B79" s="29" t="n"/>
-      <c r="C79" s="29" t="n"/>
-      <c r="D79" s="29" t="n"/>
-      <c r="E79" s="32" t="n"/>
-      <c r="F79" s="32" t="n"/>
-      <c r="G79" s="32" t="n"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" s="35">
-      <c r="A80" s="29" t="inlineStr">
+      <c r="B80" s="29" t="n"/>
+      <c r="C80" s="29" t="n"/>
+      <c r="D80" s="29" t="n"/>
+      <c r="E80" s="32" t="n"/>
+      <c r="F80" s="32" t="n"/>
+      <c r="G80" s="32" t="n"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" s="35">
+      <c r="A81" s="29" t="inlineStr">
         <is>
           <t>assigned_pm_id (SEA email address of TPM)</t>
         </is>
       </c>
-      <c r="B80" s="11" t="inlineStr">
+      <c r="B81" s="11" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="C80" s="6" t="inlineStr">
+      <c r="C81" s="6" t="inlineStr">
         <is>
           <t>not_to_be_shown</t>
         </is>
       </c>
-      <c r="D80" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E80" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F80" s="7" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G80" s="20" t="inlineStr">
+      <c r="D81" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E81" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F81" s="7" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G81" s="20" t="inlineStr">
         <is>
           <t>hilda internal purposes only</t>
         </is>
       </c>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" s="35">
-      <c r="A81" s="25" t="n"/>
-      <c r="B81" s="25" t="n"/>
-      <c r="C81" s="25" t="n"/>
-      <c r="D81" s="25" t="n"/>
-      <c r="E81" s="34" t="n"/>
-      <c r="F81" s="34" t="n"/>
-      <c r="G81" s="34" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="35">
       <c r="A82" s="25" t="n"/>
@@ -3319,16 +3347,16 @@
       <c r="F82" s="34" t="n"/>
       <c r="G82" s="34" t="n"/>
     </row>
-    <row r="83" ht="15.75" customHeight="1" s="35"/>
-    <row r="84" ht="15.75" customHeight="1" s="35">
-      <c r="A84" s="25" t="n"/>
-      <c r="B84" s="25" t="n"/>
-      <c r="C84" s="25" t="n"/>
-      <c r="D84" s="25" t="n"/>
-      <c r="E84" s="34" t="n"/>
-      <c r="F84" s="34" t="n"/>
-      <c r="G84" s="34" t="n"/>
-    </row>
+    <row r="83" ht="15.75" customHeight="1" s="35">
+      <c r="A83" s="25" t="n"/>
+      <c r="B83" s="25" t="n"/>
+      <c r="C83" s="25" t="n"/>
+      <c r="D83" s="25" t="n"/>
+      <c r="E83" s="34" t="n"/>
+      <c r="F83" s="34" t="n"/>
+      <c r="G83" s="34" t="n"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" s="35"/>
     <row r="85" ht="15.75" customHeight="1" s="35">
       <c r="A85" s="25" t="n"/>
       <c r="B85" s="25" t="n"/>
@@ -11645,6 +11673,15 @@
       <c r="F1008" s="34" t="n"/>
       <c r="G1008" s="34" t="n"/>
     </row>
+    <row r="1009">
+      <c r="A1009" s="25" t="n"/>
+      <c r="B1009" s="25" t="n"/>
+      <c r="C1009" s="25" t="n"/>
+      <c r="D1009" s="25" t="n"/>
+      <c r="E1009" s="34" t="n"/>
+      <c r="F1009" s="34" t="n"/>
+      <c r="G1009" s="34" t="n"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G48" r:id="rId1"/>

--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -2341,7 +2341,7 @@
       </c>
       <c r="G50" s="21" t="inlineStr">
         <is>
-          <t>(pending / complete / not_required); for hilda purposes only</t>
+          <t>4-value Choice enum: (pending / complete / not_required / failed). HILDA-managed; for HILDA purposes only — not shown in SP UI. Lifecycle per FR-53 I14/I15: pending = at least one received doc has review not yet complete (default at row creation when review_required=true); complete = ALL received docs reviewed (each DocumentIndexRow.llm_review_findings non-null) — required to satisfy FR-7 OwnerClosed guard condition (2) for items passing through OwnerClosed; not_required = review_required=false on item; failed = at least one received doc has persistent LLM review failure (added 2026-06-16 per FR-53 I8). SP UI engineer does NOT read or write this column.</t>
         </is>
       </c>
     </row>

--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -822,7 +822,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>YES/TPM</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -837,8 +837,7 @@
       </c>
       <c r="G8" s="36" t="inlineStr">
         <is>
-          <t>11-value Choice (Not Started, Open, OutreachSent, DocumentReceived, UnderPMReview, OwnerClosed, Delayed, Blocked, ReadyForSubmission, SubmittedToCustomer, Closed). list-value = 'Not Started' is SP-side state for TPM-loaded-template-not-yet-started-tracking;
-SP UI engineer uses this field to show start collection button, close all items button in milestone view, display approve button, send reminder button, documents button in per-work-item view</t>
+          <t>11-value Choice (Not Started, Open, OutreachSent, DocumentReceived, UnderPMReview, OwnerClosed, Delayed, Blocked, ReadyForSubmission, SubmittedToCustomer, Closed). list-value = 'Not Started' is SP-side state for TPM-loaded-template-not-yet-started-tracking; SP UI engineer uses this field to show start collection button, close all items button in milestone view, display approve button, send reminder button, documents button in per-work-item view. WRITABLE BY TPM via cell-edit (per FR-14 + FR-56 I2 lock 2026-06-16) — but RESERVED for two residual use cases only: (1) setting Delayed/Blocked from an active state when TPM observes external delay/blocker before owner reports; (2) rolling back an erroneously-fired automated transition (e.g., wrongly-advanced ReadyForSubmission). All OTHER state changes go via dedicated per-row buttons (Approve, Mark Closed, Confirm Carrier Acceptance, Resume from Delayed/Blocked) per SP_UI_button_actions.md Part 1. HILDA's sp_alert_parser auto-manages prior_delivery_state per FR-7 I2 / FR-12 / FR-14 discipline on Delayed/Blocked transitions.</t>
         </is>
       </c>
     </row>

--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -542,7 +542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1004"/>
+  <dimension ref="A1:Z1006"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="47" customWidth="1" style="40" min="1" max="1"/>
@@ -4069,102 +4069,87 @@
       <c r="Z64" s="5" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="40">
-      <c r="A65" s="32" t="n"/>
-      <c r="B65" s="14" t="n"/>
-      <c r="C65" s="32" t="n"/>
-      <c r="D65" s="32" t="n"/>
-      <c r="E65" s="33" t="n"/>
-      <c r="F65" s="33" t="n"/>
-      <c r="G65" s="33" t="n"/>
-      <c r="H65" s="5" t="n"/>
-      <c r="I65" s="5" t="n"/>
-      <c r="J65" s="5" t="n"/>
-      <c r="K65" s="5" t="n"/>
-      <c r="L65" s="5" t="n"/>
-      <c r="M65" s="5" t="n"/>
-      <c r="N65" s="5" t="n"/>
-      <c r="O65" s="5" t="n"/>
-      <c r="P65" s="5" t="n"/>
-      <c r="Q65" s="5" t="n"/>
-      <c r="R65" s="5" t="n"/>
-      <c r="S65" s="5" t="n"/>
-      <c r="T65" s="5" t="n"/>
-      <c r="U65" s="5" t="n"/>
-      <c r="V65" s="5" t="n"/>
-      <c r="W65" s="5" t="n"/>
-      <c r="X65" s="5" t="n"/>
-      <c r="Y65" s="5" t="n"/>
-      <c r="Z65" s="5" t="n"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>jira_open_ticket_count</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>[Ph-2 ONLY] HILDA-written; SP UI displays ONLY on items with tracking_modality = [CustomerJIRA] alone per FR-25 (b); deferred to Ph-2</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="40">
-      <c r="A66" s="34" t="inlineStr">
-        <is>
-          <t>Milestone SP List
-* clean separation from delivery items, avoid hacks</t>
-        </is>
-      </c>
-      <c r="B66" s="36" t="n"/>
-      <c r="C66" s="36" t="n"/>
-      <c r="D66" s="36" t="n"/>
-      <c r="E66" s="30" t="n"/>
-      <c r="F66" s="30" t="n"/>
-      <c r="G66" s="30" t="n"/>
-      <c r="H66" s="5" t="n"/>
-      <c r="I66" s="5" t="n"/>
-      <c r="J66" s="5" t="n"/>
-      <c r="K66" s="5" t="n"/>
-      <c r="L66" s="5" t="n"/>
-      <c r="M66" s="5" t="n"/>
-      <c r="N66" s="5" t="n"/>
-      <c r="O66" s="5" t="n"/>
-      <c r="P66" s="5" t="n"/>
-      <c r="Q66" s="5" t="n"/>
-      <c r="R66" s="5" t="n"/>
-      <c r="S66" s="5" t="n"/>
-      <c r="T66" s="5" t="n"/>
-      <c r="U66" s="5" t="n"/>
-      <c r="V66" s="5" t="n"/>
-      <c r="W66" s="5" t="n"/>
-      <c r="X66" s="5" t="n"/>
-      <c r="Y66" s="5" t="n"/>
-      <c r="Z66" s="5" t="n"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>jira_ticket_summary_json</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>[Ph-2 ONLY] HILDA-written JSON ticket summary; SP UI parses + displays ONLY on JIRA-only items per FR-25 (b); deferred to Ph-2</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="40">
-      <c r="A67" s="36" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="B67" s="14" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="C67" s="16" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D67" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E67" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F67" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G67" s="30" t="inlineStr">
-        <is>
-          <t>e.g. MMK, VZW</t>
-        </is>
-      </c>
+      <c r="A67" s="32" t="n"/>
+      <c r="B67" s="14" t="n"/>
+      <c r="C67" s="32" t="n"/>
+      <c r="D67" s="32" t="n"/>
+      <c r="E67" s="33" t="n"/>
+      <c r="F67" s="33" t="n"/>
+      <c r="G67" s="33" t="n"/>
       <c r="H67" s="5" t="n"/>
       <c r="I67" s="5" t="n"/>
       <c r="J67" s="5" t="n"/>
@@ -4186,36 +4171,17 @@
       <c r="Z67" s="5" t="n"/>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="40">
-      <c r="A68" s="36" t="inlineStr">
-        <is>
-          <t>project_id</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="C68" s="16" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D68" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E68" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F68" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
+      <c r="A68" s="34" t="inlineStr">
+        <is>
+          <t>Milestone SP List
+* clean separation from delivery items, avoid hacks</t>
+        </is>
+      </c>
+      <c r="B68" s="36" t="n"/>
+      <c r="C68" s="36" t="n"/>
+      <c r="D68" s="36" t="n"/>
+      <c r="E68" s="30" t="n"/>
+      <c r="F68" s="30" t="n"/>
       <c r="G68" s="30" t="n"/>
       <c r="H68" s="5" t="n"/>
       <c r="I68" s="5" t="n"/>
@@ -4240,7 +4206,7 @@
     <row r="69" ht="15.75" customHeight="1" s="40">
       <c r="A69" s="36" t="inlineStr">
         <is>
-          <t>project_model</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
@@ -4268,7 +4234,11 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G69" s="30" t="n"/>
+      <c r="G69" s="30" t="inlineStr">
+        <is>
+          <t>e.g. MMK, VZW</t>
+        </is>
+      </c>
       <c r="H69" s="5" t="n"/>
       <c r="I69" s="5" t="n"/>
       <c r="J69" s="5" t="n"/>
@@ -4292,7 +4262,7 @@
     <row r="70" ht="15.75" customHeight="1" s="40">
       <c r="A70" s="36" t="inlineStr">
         <is>
-          <t>Id</t>
+          <t>project_id</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -4320,11 +4290,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G70" s="30" t="inlineStr">
-        <is>
-          <t>PK; milestone_id</t>
-        </is>
-      </c>
+      <c r="G70" s="30" t="n"/>
       <c r="H70" s="5" t="n"/>
       <c r="I70" s="5" t="n"/>
       <c r="J70" s="5" t="n"/>
@@ -4348,7 +4314,7 @@
     <row r="71" ht="15.75" customHeight="1" s="40">
       <c r="A71" s="36" t="inlineStr">
         <is>
-          <t>Title</t>
+          <t>project_model</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -4376,11 +4342,7 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="G71" s="30" t="inlineStr">
-        <is>
-          <t>milestone_name</t>
-        </is>
-      </c>
+      <c r="G71" s="30" t="n"/>
       <c r="H71" s="5" t="n"/>
       <c r="I71" s="5" t="n"/>
       <c r="J71" s="5" t="n"/>
@@ -4404,12 +4366,12 @@
     <row r="72" ht="15.75" customHeight="1" s="40">
       <c r="A72" s="36" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Id</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>LIST</t>
+          <t>INTEGER</t>
         </is>
       </c>
       <c r="C72" s="16" t="inlineStr">
@@ -4427,14 +4389,14 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="F72" s="10" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G72" s="30" t="inlineStr">
         <is>
-          <t>list-values {Not Started, In Progress, Completed, Delayed}, SP engineer uses this to check if start collection button to be displayed in milestone view</t>
+          <t>PK; milestone_id</t>
         </is>
       </c>
       <c r="H72" s="5" t="n"/>
@@ -4460,17 +4422,17 @@
     <row r="73" ht="15.75" customHeight="1" s="40">
       <c r="A73" s="36" t="inlineStr">
         <is>
-          <t>download_package_request_timesta</t>
+          <t>Title</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
-        </is>
-      </c>
-      <c r="C73" s="15" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C73" s="16" t="inlineStr">
+        <is>
+          <t>must_show</t>
         </is>
       </c>
       <c r="D73" s="9" t="inlineStr">
@@ -4490,8 +4452,7 @@
       </c>
       <c r="G73" s="30" t="inlineStr">
         <is>
-          <t>SP engineer writes when TPM clicks Download Package button.
-The act of writing this field is what fires the SP-alert email; 'mp' dropped in the end due to size issue</t>
+          <t>milestone_name</t>
         </is>
       </c>
       <c r="H73" s="5" t="n"/>
@@ -4517,7 +4478,7 @@
     <row r="74" ht="15.75" customHeight="1" s="40">
       <c r="A74" s="36" t="inlineStr">
         <is>
-          <t>download_package_status</t>
+          <t>status</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -4535,19 +4496,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr">
+      <c r="E74" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F74" s="10" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F74" s="10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="G74" s="30" t="inlineStr">
         <is>
-          <t>HILDA-write. Enum: preparing | ready | failed. Set to preparing immediately by SP UI on click (mirror of request_timestamp); HILDA writes ready on assembly success / failed on assembly error. SP web part reads this on focus-aware refresh to decide whether to show "Preparing..." indicator or Download Now link</t>
+          <t>list-values {Not Started, In Progress, Completed, Delayed}, SP engineer uses this to check if start collection button to be displayed in milestone view</t>
         </is>
       </c>
       <c r="H74" s="5" t="n"/>
@@ -4573,12 +4534,12 @@
     <row r="75" ht="15.75" customHeight="1" s="40">
       <c r="A75" s="36" t="inlineStr">
         <is>
-          <t>download_package_url</t>
+          <t>download_package_request_timesta</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>DATE/TIME</t>
         </is>
       </c>
       <c r="C75" s="15" t="inlineStr">
@@ -4596,14 +4557,15 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="F75" s="10" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="G75" s="30" t="inlineStr">
         <is>
-          <t>HILDA-write. The scoped download URL https://hilda-proxy.corp/dl/&lt;scoped_token&gt; HILDA generates when assembly succeeds. The clickable target of the Download Now link. Null until status=ready</t>
+          <t>SP engineer writes when TPM clicks Download Package button.
+The act of writing this field is what fires the SP-alert email; 'mp' dropped in the end due to size issue</t>
         </is>
       </c>
       <c r="H75" s="5" t="n"/>
@@ -4629,17 +4591,17 @@
     <row r="76" ht="15.75" customHeight="1" s="40">
       <c r="A76" s="36" t="inlineStr">
         <is>
-          <t>download_package_generated_at</t>
+          <t>download_package_status</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
-        </is>
-      </c>
-      <c r="C76" s="15" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
+          <t>LIST</t>
+        </is>
+      </c>
+      <c r="C76" s="16" t="inlineStr">
+        <is>
+          <t>must_show</t>
         </is>
       </c>
       <c r="D76" s="9" t="inlineStr">
@@ -4647,19 +4609,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E76" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F76" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
+      <c r="E76" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F76" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
         </is>
       </c>
       <c r="G76" s="30" t="inlineStr">
         <is>
-          <t>HILDA-write. Timestamp of assembly completion; used for cache-staleness display ("generated 3 min ago")</t>
+          <t>HILDA-write. Enum: preparing | ready | failed. Set to preparing immediately by SP UI on click (mirror of request_timestamp); HILDA writes ready on assembly success / failed on assembly error. SP web part reads this on focus-aware refresh to decide whether to show "Preparing..." indicator or Download Now link</t>
         </is>
       </c>
       <c r="H76" s="5" t="n"/>
@@ -4685,12 +4647,12 @@
     <row r="77" ht="15.75" customHeight="1" s="40">
       <c r="A77" s="36" t="inlineStr">
         <is>
-          <t>milestone_collection_started_at</t>
+          <t>download_package_url</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
+          <t>STR</t>
         </is>
       </c>
       <c r="C77" s="15" t="inlineStr">
@@ -4703,19 +4665,19 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E77" s="10" t="inlineStr">
+      <c r="E77" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F77" s="10" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F77" s="10" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
       <c r="G77" s="30" t="inlineStr">
         <is>
-          <t>SP engineer uses this to check if start collection button to be displayed in milestone view. SP engineer modifies this field once collection started. The act of writing this field is what fires the SP-alert email</t>
+          <t>HILDA-write. The scoped download URL https://hilda-proxy.corp/dl/&lt;scoped_token&gt; HILDA generates when assembly succeeds. The clickable target of the Download Now link. Null until status=ready</t>
         </is>
       </c>
       <c r="H77" s="5" t="n"/>
@@ -4741,7 +4703,7 @@
     <row r="78" ht="15.75" customHeight="1" s="40">
       <c r="A78" s="36" t="inlineStr">
         <is>
-          <t>milestone_submission_triggered_a</t>
+          <t>download_package_generated_at</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -4759,9 +4721,9 @@
           <t>NO</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr">
-        <is>
-          <t>YES</t>
+      <c r="E78" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
@@ -4771,7 +4733,7 @@
       </c>
       <c r="G78" s="30" t="inlineStr">
         <is>
-          <t>SP engineer modifies this field once submit to carrier button is clicked. The act of writing this field is what fires the SP-alert email. 't' dropped in the end</t>
+          <t>HILDA-write. Timestamp of assembly completion; used for cache-staleness display ("generated 3 min ago")</t>
         </is>
       </c>
       <c r="H78" s="5" t="n"/>
@@ -4797,29 +4759,29 @@
     <row r="79" ht="15.75" customHeight="1" s="40">
       <c r="A79" s="36" t="inlineStr">
         <is>
-          <t>target_date</t>
+          <t>milestone_collection_started_at</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>DATE</t>
-        </is>
-      </c>
-      <c r="C79" s="16" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D79" s="10" t="inlineStr">
+          <t>DATE/TIME</t>
+        </is>
+      </c>
+      <c r="C79" s="15" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E79" s="10" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="F79" s="10" t="inlineStr">
         <is>
           <t>YES</t>
@@ -4827,7 +4789,7 @@
       </c>
       <c r="G79" s="30" t="inlineStr">
         <is>
-          <t>update expected_completion_date of all delivery items / work items of this milestone. The act of writing this field is what fires the SP-alert email</t>
+          <t>SP engineer uses this to check if start collection button to be displayed in milestone view. SP engineer modifies this field once collection started. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
       <c r="H79" s="5" t="n"/>
@@ -4853,7 +4815,7 @@
     <row r="80" ht="15.75" customHeight="1" s="40">
       <c r="A80" s="36" t="inlineStr">
         <is>
-          <t>refresh_requested_at</t>
+          <t>milestone_submission_triggered_a</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -4883,7 +4845,7 @@
       </c>
       <c r="G80" s="30" t="inlineStr">
         <is>
-          <t>SP engineer modifies this field once refresh button is clicked. The act of writing this field is what fires the SP-alert email</t>
+          <t>SP engineer modifies this field once submit to carrier button is clicked. The act of writing this field is what fires the SP-alert email. 't' dropped in the end</t>
         </is>
       </c>
       <c r="H80" s="5" t="n"/>
@@ -4909,37 +4871,37 @@
     <row r="81" ht="15.75" customHeight="1" s="40">
       <c r="A81" s="36" t="inlineStr">
         <is>
-          <t>closed_all_items_triggered_at</t>
+          <t>target_date</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>DATE/TIME</t>
-        </is>
-      </c>
-      <c r="C81" s="15" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="inlineStr">
+          <t>DATE</t>
+        </is>
+      </c>
+      <c r="C81" s="16" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D81" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="E81" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E81" s="10" t="inlineStr">
+      <c r="F81" s="10" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="F81" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
       <c r="G81" s="30" t="inlineStr">
         <is>
-          <t>SP engineer modifies this field once close all items button is clicked. The act of writing this field is what fires the SP-alert email</t>
+          <t>update expected_completion_date of all delivery items / work items of this milestone. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
       <c r="H81" s="5" t="n"/>
@@ -4963,39 +4925,39 @@
       <c r="Z81" s="5" t="n"/>
     </row>
     <row r="82" ht="15.75" customHeight="1" s="40">
-      <c r="A82" s="32" t="inlineStr">
-        <is>
-          <t>milestone_completion_pct</t>
-        </is>
-      </c>
-      <c r="B82" s="32" t="inlineStr">
-        <is>
-          <t>PERCENTAGE</t>
-        </is>
-      </c>
-      <c r="C82" s="32" t="inlineStr">
-        <is>
-          <t>must_show</t>
-        </is>
-      </c>
-      <c r="D82" s="32" t="inlineStr">
+      <c r="A82" s="36" t="inlineStr">
+        <is>
+          <t>refresh_requested_at</t>
+        </is>
+      </c>
+      <c r="B82" s="14" t="inlineStr">
+        <is>
+          <t>DATE/TIME</t>
+        </is>
+      </c>
+      <c r="C82" s="15" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E82" s="37" t="inlineStr">
+      <c r="E82" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F82" s="37" t="inlineStr">
-        <is>
-          <t>YES</t>
-        </is>
-      </c>
-      <c r="G82" s="37" t="inlineStr">
-        <is>
-          <t>HILDA-computed per FR-6 precedence ladder; written via [D-064] REST on every DI state change or daily_status_tick; displayed in milestone view banner</t>
+      <c r="G82" s="30" t="inlineStr">
+        <is>
+          <t>SP engineer modifies this field once refresh button is clicked. The act of writing this field is what fires the SP-alert email</t>
         </is>
       </c>
       <c r="H82" s="5" t="n"/>
@@ -5019,17 +4981,41 @@
       <c r="Z82" s="5" t="n"/>
     </row>
     <row r="83" ht="15.75" customHeight="1" s="40">
-      <c r="A83" s="38" t="inlineStr">
-        <is>
-          <t>Project List</t>
-        </is>
-      </c>
-      <c r="B83" s="36" t="n"/>
-      <c r="C83" s="36" t="n"/>
-      <c r="D83" s="36" t="n"/>
-      <c r="E83" s="39" t="n"/>
-      <c r="F83" s="39" t="n"/>
-      <c r="G83" s="39" t="n"/>
+      <c r="A83" s="36" t="inlineStr">
+        <is>
+          <t>closed_all_items_triggered_at</t>
+        </is>
+      </c>
+      <c r="B83" s="14" t="inlineStr">
+        <is>
+          <t>DATE/TIME</t>
+        </is>
+      </c>
+      <c r="C83" s="15" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E83" s="10" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G83" s="30" t="inlineStr">
+        <is>
+          <t>SP engineer modifies this field once close all items button is clicked. The act of writing this field is what fires the SP-alert email</t>
+        </is>
+      </c>
       <c r="H83" s="5" t="n"/>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="5" t="n"/>
@@ -5051,37 +5037,41 @@
       <c r="Z83" s="5" t="n"/>
     </row>
     <row r="84" ht="15.75" customHeight="1" s="40">
-      <c r="A84" s="36" t="inlineStr">
-        <is>
-          <t>project_id</t>
-        </is>
-      </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>INTEGER</t>
-        </is>
-      </c>
-      <c r="C84" s="16" t="inlineStr">
+      <c r="A84" s="32" t="inlineStr">
+        <is>
+          <t>milestone_completion_pct</t>
+        </is>
+      </c>
+      <c r="B84" s="32" t="inlineStr">
+        <is>
+          <t>PERCENTAGE</t>
+        </is>
+      </c>
+      <c r="C84" s="32" t="inlineStr">
         <is>
           <t>must_show</t>
         </is>
       </c>
-      <c r="D84" s="9" t="inlineStr">
+      <c r="D84" s="32" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E84" s="9" t="inlineStr">
+      <c r="E84" s="37" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F84" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G84" s="30" t="n"/>
+      <c r="F84" s="37" t="inlineStr">
+        <is>
+          <t>YES</t>
+        </is>
+      </c>
+      <c r="G84" s="37" t="inlineStr">
+        <is>
+          <t>HILDA-computed per FR-6 precedence ladder; written via [D-064] REST on every DI state change or daily_status_tick; displayed in milestone view banner</t>
+        </is>
+      </c>
       <c r="H84" s="5" t="n"/>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="5" t="n"/>
@@ -5103,41 +5093,17 @@
       <c r="Z84" s="5" t="n"/>
     </row>
     <row r="85" ht="15.75" customHeight="1" s="40">
-      <c r="A85" s="36" t="inlineStr">
-        <is>
-          <t>TPM</t>
-        </is>
-      </c>
-      <c r="B85" s="14" t="inlineStr">
-        <is>
-          <t>STR</t>
-        </is>
-      </c>
-      <c r="C85" s="15" t="inlineStr">
-        <is>
-          <t>not_to_be_shown</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="E85" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="F85" s="9" t="inlineStr">
-        <is>
-          <t>NO</t>
-        </is>
-      </c>
-      <c r="G85" s="30" t="inlineStr">
-        <is>
-          <t>assigned_pm_id</t>
-        </is>
-      </c>
+      <c r="A85" s="38" t="inlineStr">
+        <is>
+          <t>Project List</t>
+        </is>
+      </c>
+      <c r="B85" s="36" t="n"/>
+      <c r="C85" s="36" t="n"/>
+      <c r="D85" s="36" t="n"/>
+      <c r="E85" s="39" t="n"/>
+      <c r="F85" s="39" t="n"/>
+      <c r="G85" s="39" t="n"/>
       <c r="H85" s="5" t="n"/>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="5" t="n"/>
@@ -5159,13 +5125,37 @@
       <c r="Z85" s="5" t="n"/>
     </row>
     <row r="86" ht="15.75" customHeight="1" s="40">
-      <c r="A86" s="32" t="n"/>
-      <c r="B86" s="32" t="n"/>
-      <c r="C86" s="32" t="n"/>
-      <c r="D86" s="32" t="n"/>
-      <c r="E86" s="33" t="n"/>
-      <c r="F86" s="33" t="n"/>
-      <c r="G86" s="33" t="n"/>
+      <c r="A86" s="36" t="inlineStr">
+        <is>
+          <t>project_id</t>
+        </is>
+      </c>
+      <c r="B86" s="14" t="inlineStr">
+        <is>
+          <t>INTEGER</t>
+        </is>
+      </c>
+      <c r="C86" s="16" t="inlineStr">
+        <is>
+          <t>must_show</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G86" s="30" t="n"/>
       <c r="H86" s="5" t="n"/>
       <c r="I86" s="5" t="n"/>
       <c r="J86" s="5" t="n"/>
@@ -5187,13 +5177,41 @@
       <c r="Z86" s="5" t="n"/>
     </row>
     <row r="87" ht="15.75" customHeight="1" s="40">
-      <c r="A87" s="32" t="n"/>
-      <c r="B87" s="32" t="n"/>
-      <c r="C87" s="32" t="n"/>
-      <c r="D87" s="32" t="n"/>
-      <c r="E87" s="33" t="n"/>
-      <c r="F87" s="33" t="n"/>
-      <c r="G87" s="33" t="n"/>
+      <c r="A87" s="36" t="inlineStr">
+        <is>
+          <t>TPM</t>
+        </is>
+      </c>
+      <c r="B87" s="14" t="inlineStr">
+        <is>
+          <t>STR</t>
+        </is>
+      </c>
+      <c r="C87" s="15" t="inlineStr">
+        <is>
+          <t>not_to_be_shown</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="E87" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G87" s="30" t="inlineStr">
+        <is>
+          <t>assigned_pm_id</t>
+        </is>
+      </c>
       <c r="H87" s="5" t="n"/>
       <c r="I87" s="5" t="n"/>
       <c r="J87" s="5" t="n"/>
@@ -5215,13 +5233,13 @@
       <c r="Z87" s="5" t="n"/>
     </row>
     <row r="88" ht="15.75" customHeight="1" s="40">
-      <c r="A88" s="5" t="n"/>
-      <c r="B88" s="5" t="n"/>
-      <c r="C88" s="5" t="n"/>
-      <c r="D88" s="5" t="n"/>
-      <c r="E88" s="5" t="n"/>
-      <c r="F88" s="5" t="n"/>
-      <c r="G88" s="5" t="n"/>
+      <c r="A88" s="32" t="n"/>
+      <c r="B88" s="32" t="n"/>
+      <c r="C88" s="32" t="n"/>
+      <c r="D88" s="32" t="n"/>
+      <c r="E88" s="33" t="n"/>
+      <c r="F88" s="33" t="n"/>
+      <c r="G88" s="33" t="n"/>
       <c r="H88" s="5" t="n"/>
       <c r="I88" s="5" t="n"/>
       <c r="J88" s="5" t="n"/>
@@ -5271,13 +5289,13 @@
       <c r="Z89" s="5" t="n"/>
     </row>
     <row r="90" ht="15.75" customHeight="1" s="40">
-      <c r="A90" s="32" t="n"/>
-      <c r="B90" s="32" t="n"/>
-      <c r="C90" s="32" t="n"/>
-      <c r="D90" s="32" t="n"/>
-      <c r="E90" s="33" t="n"/>
-      <c r="F90" s="33" t="n"/>
-      <c r="G90" s="33" t="n"/>
+      <c r="A90" s="5" t="n"/>
+      <c r="B90" s="5" t="n"/>
+      <c r="C90" s="5" t="n"/>
+      <c r="D90" s="5" t="n"/>
+      <c r="E90" s="5" t="n"/>
+      <c r="F90" s="5" t="n"/>
+      <c r="G90" s="5" t="n"/>
       <c r="H90" s="5" t="n"/>
       <c r="I90" s="5" t="n"/>
       <c r="J90" s="5" t="n"/>
@@ -10759,13 +10777,13 @@
       <c r="Z285" s="5" t="n"/>
     </row>
     <row r="286" ht="15.75" customHeight="1" s="40">
-      <c r="A286" s="5" t="n"/>
-      <c r="B286" s="5" t="n"/>
-      <c r="C286" s="5" t="n"/>
-      <c r="D286" s="5" t="n"/>
-      <c r="E286" s="5" t="n"/>
-      <c r="F286" s="5" t="n"/>
-      <c r="G286" s="5" t="n"/>
+      <c r="A286" s="32" t="n"/>
+      <c r="B286" s="32" t="n"/>
+      <c r="C286" s="32" t="n"/>
+      <c r="D286" s="32" t="n"/>
+      <c r="E286" s="33" t="n"/>
+      <c r="F286" s="33" t="n"/>
+      <c r="G286" s="33" t="n"/>
       <c r="H286" s="5" t="n"/>
       <c r="I286" s="5" t="n"/>
       <c r="J286" s="5" t="n"/>
@@ -10787,13 +10805,13 @@
       <c r="Z286" s="5" t="n"/>
     </row>
     <row r="287" ht="15.75" customHeight="1" s="40">
-      <c r="A287" s="5" t="n"/>
-      <c r="B287" s="5" t="n"/>
-      <c r="C287" s="5" t="n"/>
-      <c r="D287" s="5" t="n"/>
-      <c r="E287" s="5" t="n"/>
-      <c r="F287" s="5" t="n"/>
-      <c r="G287" s="5" t="n"/>
+      <c r="A287" s="32" t="n"/>
+      <c r="B287" s="32" t="n"/>
+      <c r="C287" s="32" t="n"/>
+      <c r="D287" s="32" t="n"/>
+      <c r="E287" s="33" t="n"/>
+      <c r="F287" s="33" t="n"/>
+      <c r="G287" s="33" t="n"/>
       <c r="H287" s="5" t="n"/>
       <c r="I287" s="5" t="n"/>
       <c r="J287" s="5" t="n"/>
@@ -30890,6 +30908,62 @@
       <c r="Y1004" s="5" t="n"/>
       <c r="Z1004" s="5" t="n"/>
     </row>
+    <row r="1005">
+      <c r="A1005" s="5" t="n"/>
+      <c r="B1005" s="5" t="n"/>
+      <c r="C1005" s="5" t="n"/>
+      <c r="D1005" s="5" t="n"/>
+      <c r="E1005" s="5" t="n"/>
+      <c r="F1005" s="5" t="n"/>
+      <c r="G1005" s="5" t="n"/>
+      <c r="H1005" s="5" t="n"/>
+      <c r="I1005" s="5" t="n"/>
+      <c r="J1005" s="5" t="n"/>
+      <c r="K1005" s="5" t="n"/>
+      <c r="L1005" s="5" t="n"/>
+      <c r="M1005" s="5" t="n"/>
+      <c r="N1005" s="5" t="n"/>
+      <c r="O1005" s="5" t="n"/>
+      <c r="P1005" s="5" t="n"/>
+      <c r="Q1005" s="5" t="n"/>
+      <c r="R1005" s="5" t="n"/>
+      <c r="S1005" s="5" t="n"/>
+      <c r="T1005" s="5" t="n"/>
+      <c r="U1005" s="5" t="n"/>
+      <c r="V1005" s="5" t="n"/>
+      <c r="W1005" s="5" t="n"/>
+      <c r="X1005" s="5" t="n"/>
+      <c r="Y1005" s="5" t="n"/>
+      <c r="Z1005" s="5" t="n"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" s="5" t="n"/>
+      <c r="B1006" s="5" t="n"/>
+      <c r="C1006" s="5" t="n"/>
+      <c r="D1006" s="5" t="n"/>
+      <c r="E1006" s="5" t="n"/>
+      <c r="F1006" s="5" t="n"/>
+      <c r="G1006" s="5" t="n"/>
+      <c r="H1006" s="5" t="n"/>
+      <c r="I1006" s="5" t="n"/>
+      <c r="J1006" s="5" t="n"/>
+      <c r="K1006" s="5" t="n"/>
+      <c r="L1006" s="5" t="n"/>
+      <c r="M1006" s="5" t="n"/>
+      <c r="N1006" s="5" t="n"/>
+      <c r="O1006" s="5" t="n"/>
+      <c r="P1006" s="5" t="n"/>
+      <c r="Q1006" s="5" t="n"/>
+      <c r="R1006" s="5" t="n"/>
+      <c r="S1006" s="5" t="n"/>
+      <c r="T1006" s="5" t="n"/>
+      <c r="U1006" s="5" t="n"/>
+      <c r="V1006" s="5" t="n"/>
+      <c r="W1006" s="5" t="n"/>
+      <c r="X1006" s="5" t="n"/>
+      <c r="Y1006" s="5" t="n"/>
+      <c r="Z1006" s="5" t="n"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G50" r:id="rId1"/>

--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -4069,74 +4069,74 @@
       <c r="Z64" s="5" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="40">
-      <c r="A65" t="inlineStr">
+      <c r="A65" s="0" t="inlineStr">
         <is>
           <t>jira_open_ticket_count</t>
         </is>
       </c>
-      <c r="B65" t="inlineStr">
+      <c r="B65" s="0" t="inlineStr">
         <is>
           <t>INTEGER</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C65" s="0" t="inlineStr">
         <is>
           <t>must_show</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D65" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E65" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="0" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="G65" s="0" t="inlineStr">
         <is>
           <t>[Ph-2 ONLY] HILDA-written; SP UI displays ONLY on items with tracking_modality = [CustomerJIRA] alone per FR-25 (b); deferred to Ph-2</t>
         </is>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="40">
-      <c r="A66" t="inlineStr">
+      <c r="A66" s="0" t="inlineStr">
         <is>
           <t>jira_ticket_summary_json</t>
         </is>
       </c>
-      <c r="B66" t="inlineStr">
+      <c r="B66" s="0" t="inlineStr">
         <is>
           <t>STR</t>
         </is>
       </c>
-      <c r="C66" t="inlineStr">
+      <c r="C66" s="0" t="inlineStr">
         <is>
           <t>must_show</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
+      <c r="D66" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E66" s="0" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="0" t="inlineStr">
         <is>
           <t>YES</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="G66" s="0" t="inlineStr">
         <is>
           <t>[Ph-2 ONLY] HILDA-written JSON ticket summary; SP UI parses + displays ONLY on JIRA-only items per FR-25 (b); deferred to Ph-2</t>
         </is>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>STR</t>
+          <t>Person/Group</t>
         </is>
       </c>
       <c r="C87" s="15" t="inlineStr">

--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -595,7 +595,11 @@
           <t>Notes for SP UI Engineer</t>
         </is>
       </c>
-      <c r="H1" s="5" t="n"/>
+      <c r="H1" s="5" t="inlineStr">
+        <is>
+          <t>LIST values (Choice enums)</t>
+        </is>
+      </c>
       <c r="I1" s="5" t="n"/>
       <c r="J1" s="5" t="n"/>
       <c r="K1" s="5" t="n"/>
@@ -1130,7 +1134,11 @@
 delivery_item_type : what type of document being delivered</t>
         </is>
       </c>
-      <c r="H11" s="5" t="n"/>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>Confirmation, TEST_TECH_WAIVER_REPORT, COMPLIANCE_CERTIFICATION_RELEASE_NOTES, Default (4 values per FR-7)</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="n"/>
       <c r="J11" s="5" t="n"/>
       <c r="K11" s="5" t="n"/>
@@ -1186,7 +1194,11 @@
           <t>11-value Choice (Not Started, Open, OutreachSent, DocumentReceived, UnderPMReview, OwnerClosed, Delayed, Blocked, ReadyForSubmission, SubmittedToCustomer, Closed). list-value = 'Not Started' is SP-side state for TPM-loaded-template-not-yet-started-tracking; SP UI engineer uses this field to show start collection button, close all items button in milestone view, display approve button, send reminder button, documents button in per-work-item view. WRITABLE BY TPM via cell-edit (per FR-14 + FR-56 I2 lock 2026-06-16) — but RESERVED for two residual use cases only: (1) setting Delayed/Blocked from an active state when TPM observes external delay/blocker before owner reports; (2) rolling back an erroneously-fired automated transition (e.g., wrongly-advanced ReadyForSubmission). All OTHER state changes go via dedicated per-row buttons (Approve, Mark Closed, Confirm Carrier Acceptance, Resume from Delayed/Blocked) per SP_UI_button_actions.md Part 1. HILDA's sp_alert_parser auto-manages prior_delivery_state per FR-7 I2 / FR-12 / FR-14 discipline on Delayed/Blocked transitions.</t>
         </is>
       </c>
-      <c r="H12" s="5" t="n"/>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>Not Started, Open, OutreachSent, DocumentReceived, UnderPMReview, OwnerClosed, Delayed, Blocked, ReadyForSubmission, SubmittedToCustomer, Closed (11 values per FR-7 — SP-only Not Started + 10 HILDA enum values)</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="n"/>
       <c r="J12" s="5" t="n"/>
       <c r="K12" s="5" t="n"/>
@@ -1242,7 +1254,11 @@
           <t>Same 11-value Choice enum as delivery_state. HILDA-written audit column: stores the state immediately preceding entry into 'Delayed' or 'Blocked'; set by HILDA when transitioning into Delayed/Blocked; cleared (set to NULL) when transitioning out. Enables HILDA to restore the prior active state on exit per FR-7. SP UI engineer does NOT read or write this column.</t>
         </is>
       </c>
-      <c r="H13" s="5" t="n"/>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>Same 11 values as delivery_state per FR-7 (HILDA-written; SP UI engineer does not read or write)</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="n"/>
       <c r="J13" s="5" t="n"/>
       <c r="K13" s="5" t="n"/>
@@ -1850,7 +1866,11 @@
           <t>MultiChoice {Email, CorporateMessenger, CorporatePLM, NetworkSharedDrive, Customer JIRA, SPUI} ]</t>
         </is>
       </c>
-      <c r="H24" s="5" t="n"/>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>Email, CorporateMessenger, CorporatePLM, NetworkSharedDrive, CustomerJIRA, SPUI (6 values per FR-7; multi-select)</t>
+        </is>
+      </c>
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="5" t="n"/>
       <c r="K24" s="5" t="n"/>
@@ -2010,7 +2030,11 @@
           <t>enum {SW PL, HW PL, CPM, MNO-UX, MNO-TPM, MNO-ETM, MNO-IOT, MNO-SOLUTION, MNO-OMADM, MQL-FIT, MQL, MQL PC, GPS, MNO-SELNA, APPS, MNO-DTR}</t>
         </is>
       </c>
-      <c r="H27" s="5" t="n"/>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>Per-customer; values set by template.yaml TG definitions per FR-40 (no fixed enum across customers)</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="5" t="n"/>
       <c r="K27" s="5" t="n"/>
@@ -2927,7 +2951,11 @@
           <t>values {GoogleDrive, Email, Customer tracking system}; type of system to which documents are uploaded</t>
         </is>
       </c>
-      <c r="H44" s="5" t="n"/>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>TBD — confirm with architect at SP-list-provisioning time (observed test sample: Email, CustomerTrackingSystem)</t>
+        </is>
+      </c>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="5" t="n"/>
       <c r="K44" s="5" t="n"/>
@@ -3376,7 +3404,11 @@
           <t>4-value Choice enum: (pending / complete / not_required / failed). HILDA-managed; for HILDA purposes only — not shown in SP UI. Lifecycle per FR-53 I14/I15: pending = at least one received doc has review not yet complete (default at row creation when review_required=true); complete = ALL received docs reviewed (each DocumentIndexRow.llm_review_findings non-null) — required to satisfy FR-7 OwnerClosed guard condition (2) for items passing through OwnerClosed; not_required = review_required=false on item; failed = at least one received doc has persistent LLM review failure (added 2026-06-16 per FR-53 I8). SP UI engineer does NOT read or write this column.</t>
         </is>
       </c>
-      <c r="H52" s="5" t="n"/>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>pending, complete, failed (3 values per FR-53 / FR-62 / FR-87 lifecycle)</t>
+        </is>
+      </c>
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="5" t="n"/>
       <c r="K52" s="5" t="n"/>
@@ -3825,7 +3857,11 @@
 (two different network shared drives that different TGs use)  (denorm TG)</t>
         </is>
       </c>
-      <c r="H60" s="5" t="n"/>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>none, nsd1, nsd2 (3 values per FR-13 flat per-TG folder structure)</t>
+        </is>
+      </c>
       <c r="I60" s="5" t="n"/>
       <c r="J60" s="5" t="n"/>
       <c r="K60" s="5" t="n"/>
@@ -4511,7 +4547,11 @@
           <t>list-values {Not Started, In Progress, Completed, Delayed}, SP engineer uses this to check if start collection button to be displayed in milestone view</t>
         </is>
       </c>
-      <c r="H74" s="5" t="n"/>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>Not Started, In Progress, Completed, Delayed (4 values per FR-6 precedence ladder)</t>
+        </is>
+      </c>
       <c r="I74" s="5" t="n"/>
       <c r="J74" s="5" t="n"/>
       <c r="K74" s="5" t="n"/>
@@ -4624,7 +4664,11 @@
           <t>HILDA-write. Enum: preparing | ready | failed. Set to preparing immediately by SP UI on click (mirror of request_timestamp); HILDA writes ready on assembly success / failed on assembly error. SP web part reads this on focus-aware refresh to decide whether to show "Preparing..." indicator or Download Now link</t>
         </is>
       </c>
-      <c r="H76" s="5" t="n"/>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>preparing, ready, failed (3 values per FR-73; [Ph-2] deferred)</t>
+        </is>
+      </c>
       <c r="I76" s="5" t="n"/>
       <c r="J76" s="5" t="n"/>
       <c r="K76" s="5" t="n"/>

--- a/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
+++ b/docs/sp_ui_engineer/SP_lists_authoritative.xlsx
@@ -2032,7 +2032,7 @@
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>Per-customer; values set by template.yaml TG definitions per FR-40 (no fixed enum across customers)</t>
+          <t>SW PL, HW PL, CPM, MNO-UX, MNO-TPM, MNO-ETM, MNO-IOT, MNO-SOLUTION, MNO-OMADM, MQL-FIT, MQL, MQL PC, GPS, MNO-SELNA, APPS, MNO-DTR (16 values, globally fixed across all carriers per FR-40 lock 2026-06-19)</t>
         </is>
       </c>
       <c r="I27" s="5" t="n"/>
@@ -2953,7 +2953,7 @@
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>TBD — confirm with architect at SP-list-provisioning time (observed test sample: Email, CustomerTrackingSystem)</t>
+          <t>Google Drive (1 value per FR-40 Ph-1 lock 2026-06-19; Ph-3+ may expand)</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="H52" s="5" t="inlineStr">
         <is>
-          <t>pending, complete, failed (3 values per FR-53 / FR-62 / FR-87 lifecycle)</t>
+          <t>pending, complete, not_required, failed (4 values per FR-53 / FR-62 / FR-87 lifecycle; locked 2026-06-19)</t>
         </is>
       </c>
       <c r="I52" s="5" t="n"/>
